--- a/Testcase(Guvi).xlsx
+++ b/Testcase(Guvi).xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Monika Devi\Downloads\GuviHackathon\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GuviHackathonProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E810AE1-E1F1-47B0-A29D-E94706DC41CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AAE4A56-A725-4842-A3CB-0076940252DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{19BC13FB-A341-4664-BD85-1EEB698C872B}"/>
   </bookViews>
@@ -303,9 +303,6 @@
     <t>Click "view report" for upcoming and ongoing test</t>
   </si>
   <si>
-    <t>"view report" button should is clickable</t>
-  </si>
-  <si>
     <t>Fail</t>
   </si>
   <si>
@@ -577,6 +574,9 @@
   </si>
   <si>
     <t>View report should not be clickable for upcoming and ongoing test</t>
+  </si>
+  <si>
+    <t>"view report" button is clickable</t>
   </si>
 </sst>
 </file>
@@ -1067,7 +1067,7 @@
         <v>48</v>
       </c>
       <c r="G10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
@@ -1084,7 +1084,7 @@
         <v>47</v>
       </c>
       <c r="G11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -1101,7 +1101,7 @@
         <v>44</v>
       </c>
       <c r="G12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
@@ -1118,7 +1118,7 @@
         <v>44</v>
       </c>
       <c r="G13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
@@ -1135,7 +1135,7 @@
         <v>45</v>
       </c>
       <c r="G14" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
@@ -1158,7 +1158,7 @@
         <v>44</v>
       </c>
       <c r="G16" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
@@ -1175,7 +1175,7 @@
         <v>43</v>
       </c>
       <c r="G17" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
@@ -1192,7 +1192,7 @@
         <v>42</v>
       </c>
       <c r="G18" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
@@ -1215,7 +1215,7 @@
         <v>44</v>
       </c>
       <c r="G20" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
@@ -1232,7 +1232,7 @@
         <v>52</v>
       </c>
       <c r="G21" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
@@ -1358,7 +1358,7 @@
         <v>61</v>
       </c>
       <c r="G36" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
@@ -1375,10 +1375,10 @@
         <v>63</v>
       </c>
       <c r="G37" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H37" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
@@ -1404,7 +1404,7 @@
         <v>61</v>
       </c>
       <c r="G39" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
@@ -1421,7 +1421,7 @@
         <v>68</v>
       </c>
       <c r="G40" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
@@ -1444,7 +1444,7 @@
         <v>74</v>
       </c>
       <c r="G42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
@@ -1461,7 +1461,7 @@
         <v>75</v>
       </c>
       <c r="G43" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
@@ -1484,7 +1484,7 @@
         <v>79</v>
       </c>
       <c r="G45" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
@@ -1512,7 +1512,7 @@
         <v>0</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
@@ -1520,7 +1520,7 @@
         <v>2</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
@@ -1609,7 +1609,7 @@
         <v>86</v>
       </c>
       <c r="G60" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.35">
@@ -1629,13 +1629,13 @@
         <v>73</v>
       </c>
       <c r="F62" t="s">
+        <v>180</v>
+      </c>
+      <c r="G62" t="s">
         <v>89</v>
       </c>
-      <c r="G62" t="s">
-        <v>90</v>
-      </c>
       <c r="H62" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.35">
@@ -1646,7 +1646,7 @@
         <v>3</v>
       </c>
       <c r="B64" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C64" t="s">
         <v>84</v>
@@ -1661,24 +1661,24 @@
         <v>86</v>
       </c>
       <c r="G64" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C65" t="s">
+        <v>91</v>
+      </c>
+      <c r="D65" t="s">
+        <v>28</v>
+      </c>
+      <c r="E65" t="s">
         <v>92</v>
       </c>
-      <c r="D65" t="s">
-        <v>28</v>
-      </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
         <v>93</v>
       </c>
-      <c r="F65" t="s">
-        <v>94</v>
-      </c>
       <c r="G65" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
@@ -1686,7 +1686,7 @@
         <v>4</v>
       </c>
       <c r="B67" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C67" t="s">
         <v>84</v>
@@ -1701,24 +1701,24 @@
         <v>86</v>
       </c>
       <c r="G67" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C68" t="s">
+        <v>95</v>
+      </c>
+      <c r="D68" t="s">
+        <v>28</v>
+      </c>
+      <c r="E68" t="s">
         <v>96</v>
       </c>
-      <c r="D68" t="s">
-        <v>28</v>
-      </c>
-      <c r="E68" t="s">
+      <c r="F68" t="s">
         <v>97</v>
       </c>
-      <c r="F68" t="s">
-        <v>98</v>
-      </c>
       <c r="G68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
@@ -1746,7 +1746,7 @@
         <v>0</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
@@ -1754,7 +1754,7 @@
         <v>2</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
@@ -1828,107 +1828,107 @@
         <v>1</v>
       </c>
       <c r="B83" t="s">
+        <v>100</v>
+      </c>
+      <c r="C83" t="s">
         <v>101</v>
       </c>
-      <c r="C83" t="s">
-        <v>102</v>
-      </c>
       <c r="D83" t="s">
         <v>28</v>
       </c>
       <c r="E83" t="s">
+        <v>107</v>
+      </c>
+      <c r="F83" t="s">
         <v>108</v>
       </c>
-      <c r="F83" t="s">
-        <v>109</v>
-      </c>
       <c r="G83" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C84" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D84" t="s">
         <v>28</v>
       </c>
       <c r="E84" t="s">
+        <v>109</v>
+      </c>
+      <c r="F84" t="s">
         <v>110</v>
       </c>
-      <c r="F84" t="s">
-        <v>111</v>
-      </c>
       <c r="G84" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C85" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D85" t="s">
         <v>28</v>
       </c>
       <c r="E85" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F85" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G85" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C86" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D86" t="s">
         <v>28</v>
       </c>
       <c r="E86" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F86" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G86" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C87" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D87" t="s">
         <v>28</v>
       </c>
       <c r="E87" t="s">
+        <v>115</v>
+      </c>
+      <c r="F87" t="s">
         <v>116</v>
       </c>
-      <c r="F87" t="s">
-        <v>117</v>
-      </c>
       <c r="G87" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C88" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D88" t="s">
         <v>28</v>
       </c>
       <c r="E88" t="s">
+        <v>117</v>
+      </c>
+      <c r="F88" t="s">
         <v>118</v>
       </c>
-      <c r="F88" t="s">
-        <v>119</v>
-      </c>
       <c r="G88" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.35">
@@ -1956,7 +1956,7 @@
         <v>0</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.35">
@@ -1964,7 +1964,7 @@
         <v>2</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.35">
@@ -2038,73 +2038,73 @@
         <v>1</v>
       </c>
       <c r="B103" t="s">
+        <v>121</v>
+      </c>
+      <c r="C103" t="s">
         <v>122</v>
       </c>
-      <c r="C103" t="s">
+      <c r="D103" t="s">
+        <v>28</v>
+      </c>
+      <c r="E103" t="s">
         <v>123</v>
       </c>
-      <c r="D103" t="s">
-        <v>28</v>
-      </c>
-      <c r="E103" t="s">
-        <v>124</v>
-      </c>
       <c r="F103" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G103" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C104" t="s">
+        <v>124</v>
+      </c>
+      <c r="D104" t="s">
+        <v>28</v>
+      </c>
+      <c r="E104" t="s">
         <v>125</v>
       </c>
-      <c r="D104" t="s">
-        <v>28</v>
-      </c>
-      <c r="E104" t="s">
-        <v>126</v>
-      </c>
       <c r="F104" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G104" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C105" t="s">
+        <v>142</v>
+      </c>
+      <c r="D105" t="s">
+        <v>145</v>
+      </c>
+      <c r="E105" t="s">
         <v>143</v>
       </c>
-      <c r="D105" t="s">
-        <v>146</v>
-      </c>
-      <c r="E105" t="s">
+      <c r="F105" t="s">
         <v>144</v>
       </c>
-      <c r="F105" t="s">
-        <v>145</v>
-      </c>
       <c r="G105" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C106" t="s">
+        <v>128</v>
+      </c>
+      <c r="D106" t="s">
+        <v>28</v>
+      </c>
+      <c r="E106" t="s">
         <v>129</v>
       </c>
-      <c r="D106" t="s">
-        <v>28</v>
-      </c>
-      <c r="E106" t="s">
+      <c r="F106" t="s">
         <v>130</v>
       </c>
-      <c r="F106" t="s">
-        <v>131</v>
-      </c>
       <c r="G106" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.35">
@@ -2112,56 +2112,56 @@
         <v>2</v>
       </c>
       <c r="B108" t="s">
+        <v>131</v>
+      </c>
+      <c r="C108" t="s">
         <v>132</v>
       </c>
-      <c r="C108" t="s">
+      <c r="D108" t="s">
         <v>133</v>
       </c>
-      <c r="D108" t="s">
-        <v>134</v>
-      </c>
       <c r="E108" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F108" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C109" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D109" t="s">
         <v>28</v>
       </c>
       <c r="E109" t="s">
+        <v>136</v>
+      </c>
+      <c r="F109" t="s">
         <v>137</v>
       </c>
-      <c r="F109" t="s">
-        <v>138</v>
-      </c>
       <c r="G109" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C110" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D110" t="s">
         <v>28</v>
       </c>
       <c r="E110" t="s">
+        <v>136</v>
+      </c>
+      <c r="F110" t="s">
         <v>137</v>
       </c>
-      <c r="F110" t="s">
-        <v>138</v>
-      </c>
       <c r="G110" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.35">
@@ -2189,7 +2189,7 @@
         <v>0</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.35">
@@ -2197,7 +2197,7 @@
         <v>2</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.35">
@@ -2271,141 +2271,141 @@
         <v>1</v>
       </c>
       <c r="B125" t="s">
+        <v>146</v>
+      </c>
+      <c r="C125" t="s">
         <v>147</v>
       </c>
-      <c r="C125" t="s">
-        <v>148</v>
-      </c>
       <c r="D125" t="s">
         <v>28</v>
       </c>
       <c r="E125" t="s">
+        <v>158</v>
+      </c>
+      <c r="F125" t="s">
         <v>159</v>
       </c>
-      <c r="F125" t="s">
-        <v>160</v>
-      </c>
       <c r="G125" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C126" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D126" t="s">
         <v>28</v>
       </c>
       <c r="E126" t="s">
+        <v>160</v>
+      </c>
+      <c r="F126" t="s">
         <v>161</v>
       </c>
-      <c r="F126" t="s">
-        <v>162</v>
-      </c>
       <c r="G126" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C127" t="s">
+        <v>149</v>
+      </c>
+      <c r="D127" t="s">
         <v>150</v>
       </c>
-      <c r="D127" t="s">
-        <v>151</v>
-      </c>
       <c r="E127" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F127" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G127" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C128" t="s">
+        <v>151</v>
+      </c>
+      <c r="D128" t="s">
         <v>152</v>
       </c>
-      <c r="D128" t="s">
-        <v>153</v>
-      </c>
       <c r="E128" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F128" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G128" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C129" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D129" t="s">
         <v>28</v>
       </c>
       <c r="E129" t="s">
+        <v>164</v>
+      </c>
+      <c r="F129" t="s">
         <v>165</v>
       </c>
-      <c r="F129" t="s">
-        <v>166</v>
-      </c>
       <c r="G129" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C130" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D130" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E130" t="s">
+        <v>166</v>
+      </c>
+      <c r="F130" t="s">
         <v>167</v>
       </c>
-      <c r="F130" t="s">
-        <v>168</v>
-      </c>
       <c r="G130" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C131" t="s">
+        <v>156</v>
+      </c>
+      <c r="D131" t="s">
         <v>157</v>
       </c>
-      <c r="D131" t="s">
-        <v>158</v>
-      </c>
       <c r="E131" t="s">
+        <v>166</v>
+      </c>
+      <c r="F131" t="s">
         <v>167</v>
       </c>
-      <c r="F131" t="s">
-        <v>168</v>
-      </c>
       <c r="G131" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C132" t="s">
+        <v>169</v>
+      </c>
+      <c r="D132" t="s">
+        <v>28</v>
+      </c>
+      <c r="E132" t="s">
         <v>170</v>
       </c>
-      <c r="D132" t="s">
-        <v>28</v>
-      </c>
-      <c r="E132" t="s">
+      <c r="F132" t="s">
         <v>171</v>
       </c>
-      <c r="F132" t="s">
-        <v>172</v>
-      </c>
       <c r="G132" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
@@ -2413,141 +2413,141 @@
         <v>2</v>
       </c>
       <c r="B134" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C134" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D134" t="s">
         <v>28</v>
       </c>
       <c r="E134" t="s">
+        <v>158</v>
+      </c>
+      <c r="F134" t="s">
         <v>159</v>
       </c>
-      <c r="F134" t="s">
-        <v>160</v>
-      </c>
       <c r="G134" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C135" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D135" t="s">
         <v>28</v>
       </c>
       <c r="E135" t="s">
+        <v>160</v>
+      </c>
+      <c r="F135" t="s">
         <v>161</v>
       </c>
-      <c r="F135" t="s">
-        <v>162</v>
-      </c>
       <c r="G135" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C136" t="s">
+        <v>149</v>
+      </c>
+      <c r="D136" t="s">
         <v>150</v>
       </c>
-      <c r="D136" t="s">
-        <v>151</v>
-      </c>
       <c r="E136" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F136" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G136" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C137" t="s">
+        <v>151</v>
+      </c>
+      <c r="D137" t="s">
         <v>152</v>
       </c>
-      <c r="D137" t="s">
-        <v>153</v>
-      </c>
       <c r="E137" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F137" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G137" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C138" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D138" t="s">
         <v>28</v>
       </c>
       <c r="E138" t="s">
+        <v>164</v>
+      </c>
+      <c r="F138" t="s">
         <v>165</v>
       </c>
-      <c r="F138" t="s">
-        <v>166</v>
-      </c>
       <c r="G138" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C139" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D139" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E139" t="s">
+        <v>166</v>
+      </c>
+      <c r="F139" t="s">
         <v>167</v>
       </c>
-      <c r="F139" t="s">
-        <v>168</v>
-      </c>
       <c r="G139" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C140" t="s">
+        <v>156</v>
+      </c>
+      <c r="D140" t="s">
         <v>157</v>
       </c>
-      <c r="D140" t="s">
-        <v>158</v>
-      </c>
       <c r="E140" t="s">
+        <v>166</v>
+      </c>
+      <c r="F140" t="s">
         <v>167</v>
       </c>
-      <c r="F140" t="s">
-        <v>168</v>
-      </c>
       <c r="G140" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C141" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D141" t="s">
         <v>28</v>
       </c>
       <c r="E141" t="s">
+        <v>173</v>
+      </c>
+      <c r="F141" t="s">
         <v>174</v>
       </c>
-      <c r="F141" t="s">
-        <v>175</v>
-      </c>
       <c r="G141" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
